--- a/grupos/6BLCM - Estadisticos 20232.xlsx
+++ b/grupos/6BLCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="90">
   <si>
     <t>Materia</t>
   </si>
@@ -203,15 +203,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -230,67 +230,64 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
+    <t>MORENO</t>
   </si>
   <si>
     <t>PERALTA</t>
   </si>
   <si>
-    <t>ZUÑIGA</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>MONGE</t>
   </si>
   <si>
-    <t>ESPINDOLA</t>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
+    <t>ROSA ITZEL</t>
   </si>
   <si>
     <t>ANDRES</t>
   </si>
   <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>AXEL EDUARDO</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
+    <t>NAHOMY</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>ROSA ITZEL</t>
   </si>
 </sst>
 </file>
@@ -798,22 +795,22 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -843,10 +840,10 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -875,22 +872,22 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -923,7 +920,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -952,22 +949,22 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -997,13 +994,13 @@
         <v>10</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1023,28 +1020,28 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1071,13 +1068,13 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1106,22 +1103,22 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1154,7 +1151,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1183,22 +1180,22 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1228,13 +1225,13 @@
         <v>10</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1260,22 +1257,22 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1308,10 +1305,10 @@
         <v>7</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1331,28 +1328,28 @@
         <v>6</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11">
         <v>5</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1385,10 +1382,10 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1414,22 +1411,22 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1459,13 +1456,13 @@
         <v>10</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1491,22 +1488,22 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1536,10 +1533,10 @@
         <v>8</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>9</v>
@@ -1568,22 +1565,22 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1604,13 +1601,13 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>7</v>
@@ -1619,7 +1616,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1645,22 +1642,22 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1690,13 +1687,13 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1716,28 +1713,28 @@
         <v>7</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G16">
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1758,10 +1755,10 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1770,7 +1767,7 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1799,22 +1796,22 @@
         <v>5</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1850,7 +1847,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1876,22 +1873,22 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1924,7 +1921,7 @@
         <v>5</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>5</v>
@@ -1953,22 +1950,22 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2001,7 +1998,7 @@
         <v>10</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -2030,22 +2027,22 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2072,13 +2069,13 @@
         <v>9</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>9</v>
@@ -2107,22 +2104,22 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2155,10 +2152,10 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2178,28 +2175,28 @@
         <v>6</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G22">
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2220,22 +2217,22 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>6</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2261,22 +2258,22 @@
         <v>7</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2303,16 +2300,16 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W23">
         <v>7</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2338,22 +2335,22 @@
         <v>9</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2383,13 +2380,13 @@
         <v>10</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2415,22 +2412,22 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2457,16 +2454,16 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>7</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2492,22 +2489,22 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2534,16 +2531,16 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2569,22 +2566,22 @@
         <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2614,13 +2611,13 @@
         <v>8</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2646,22 +2643,22 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2691,10 +2688,10 @@
         <v>10</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2723,22 +2720,22 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2765,7 +2762,7 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -2800,22 +2797,22 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2845,10 +2842,10 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -2877,22 +2874,22 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2919,7 +2916,7 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>8</v>
@@ -2928,7 +2925,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2954,22 +2951,22 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -2999,13 +2996,13 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3031,22 +3028,22 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3079,7 +3076,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3108,22 +3105,22 @@
         <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3156,10 +3153,10 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3185,22 +3182,22 @@
         <v>5</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3221,13 +3218,13 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>6</v>
@@ -3262,22 +3259,22 @@
         <v>6</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3298,22 +3295,22 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>7</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y36">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3339,22 +3336,22 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3384,10 +3381,10 @@
         <v>10</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>10</v>
@@ -3416,22 +3413,22 @@
         <v>6</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3458,7 +3455,7 @@
         <v>7</v>
       </c>
       <c r="V38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W38">
         <v>6</v>
@@ -3493,22 +3490,22 @@
         <v>9</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3538,13 +3535,13 @@
         <v>10</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y39">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3570,22 +3567,22 @@
         <v>6</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3606,10 +3603,10 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V40">
         <v>7</v>
@@ -3618,10 +3615,10 @@
         <v>5</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y40">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3816,40 +3813,40 @@
         <v>86.7</v>
       </c>
       <c r="H5">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I5">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>86.7</v>
+        <v>85.5</v>
       </c>
       <c r="N5">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O5">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>86.7</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3884,7 +3881,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3902,7 +3899,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3934,10 +3931,10 @@
         <v>90</v>
       </c>
       <c r="H7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I7">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -3949,13 +3946,13 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>90</v>
+        <v>94.5</v>
       </c>
       <c r="N7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O7">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P7">
         <v>100</v>
@@ -3967,7 +3964,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>90</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3993,40 +3990,40 @@
         <v>93.3</v>
       </c>
       <c r="H8">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="I8">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J8">
         <v>100</v>
       </c>
       <c r="K8">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N8">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="O8">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P8">
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4061,7 +4058,7 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -4079,7 +4076,7 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>98.3</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -4111,10 +4108,10 @@
         <v>93.3</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I10">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -4126,13 +4123,13 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="O10">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -4144,7 +4141,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>93.3</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4170,40 +4167,40 @@
         <v>90</v>
       </c>
       <c r="H11">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="I11">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
-        <v>90</v>
+        <v>94.5</v>
       </c>
       <c r="N11">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="O11">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>96.7</v>
+        <v>91.7</v>
       </c>
       <c r="R11">
         <v>100</v>
       </c>
       <c r="S11">
-        <v>90</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4244,7 +4241,7 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -4262,7 +4259,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4288,40 +4285,40 @@
         <v>96.7</v>
       </c>
       <c r="H13">
-        <v>90</v>
+        <v>89.8</v>
       </c>
       <c r="I13">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
+        <v>98.2</v>
+      </c>
+      <c r="N13">
+        <v>89.8</v>
+      </c>
+      <c r="O13">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="P13">
+        <v>100</v>
+      </c>
+      <c r="Q13">
         <v>96.7</v>
       </c>
-      <c r="N13">
-        <v>90</v>
-      </c>
-      <c r="O13">
-        <v>90</v>
-      </c>
-      <c r="P13">
-        <v>100</v>
-      </c>
-      <c r="Q13">
-        <v>100</v>
-      </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4347,40 +4344,40 @@
         <v>96.7</v>
       </c>
       <c r="H14">
-        <v>87.5</v>
+        <v>92</v>
       </c>
       <c r="I14">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J14">
         <v>100</v>
       </c>
       <c r="K14">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="L14">
         <v>100</v>
       </c>
       <c r="M14">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="N14">
-        <v>87.5</v>
+        <v>92</v>
       </c>
       <c r="O14">
-        <v>80</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4415,31 +4412,31 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15">
+        <v>98.2</v>
+      </c>
+      <c r="N15">
+        <v>100</v>
+      </c>
+      <c r="O15">
+        <v>100</v>
+      </c>
+      <c r="P15">
+        <v>100</v>
+      </c>
+      <c r="Q15">
         <v>96.7</v>
       </c>
-      <c r="N15">
-        <v>100</v>
-      </c>
-      <c r="O15">
-        <v>100</v>
-      </c>
-      <c r="P15">
-        <v>100</v>
-      </c>
-      <c r="Q15">
-        <v>100</v>
-      </c>
       <c r="R15">
         <v>100</v>
       </c>
       <c r="S15">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4465,40 +4462,40 @@
         <v>96.7</v>
       </c>
       <c r="H16">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I16">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L16">
         <v>100</v>
       </c>
       <c r="M16">
+        <v>98.2</v>
+      </c>
+      <c r="N16">
+        <v>97.7</v>
+      </c>
+      <c r="O16">
+        <v>95.5</v>
+      </c>
+      <c r="P16">
+        <v>100</v>
+      </c>
+      <c r="Q16">
         <v>96.7</v>
       </c>
-      <c r="N16">
-        <v>95</v>
-      </c>
-      <c r="O16">
-        <v>90</v>
-      </c>
-      <c r="P16">
-        <v>100</v>
-      </c>
-      <c r="Q16">
-        <v>100</v>
-      </c>
       <c r="R16">
         <v>100</v>
       </c>
       <c r="S16">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4583,10 +4580,10 @@
         <v>90</v>
       </c>
       <c r="H18">
-        <v>87.5</v>
+        <v>89.8</v>
       </c>
       <c r="I18">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -4598,13 +4595,13 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="N18">
-        <v>87.5</v>
+        <v>89.8</v>
       </c>
       <c r="O18">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="P18">
         <v>100</v>
@@ -4616,7 +4613,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4642,7 +4639,7 @@
         <v>86.7</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I19">
         <v>100</v>
@@ -4657,10 +4654,10 @@
         <v>100</v>
       </c>
       <c r="M19">
-        <v>86.7</v>
+        <v>92.7</v>
       </c>
       <c r="N19">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -4675,7 +4672,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>86.7</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4701,40 +4698,40 @@
         <v>96.7</v>
       </c>
       <c r="H20">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="I20">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <v>83.3</v>
+        <v>88.3</v>
       </c>
       <c r="L20">
         <v>100</v>
       </c>
       <c r="M20">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="N20">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="O20">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P20">
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>83.3</v>
+        <v>88.3</v>
       </c>
       <c r="R20">
         <v>100</v>
       </c>
       <c r="S20">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4760,40 +4757,40 @@
         <v>93.3</v>
       </c>
       <c r="H21">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="I21">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="L21">
         <v>100</v>
       </c>
       <c r="M21">
-        <v>93.3</v>
+        <v>85.5</v>
       </c>
       <c r="N21">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="O21">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>93.3</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4819,40 +4816,40 @@
         <v>86.7</v>
       </c>
       <c r="H22">
-        <v>87.5</v>
+        <v>85.2</v>
       </c>
       <c r="I22">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="L22">
         <v>100</v>
       </c>
       <c r="M22">
-        <v>86.7</v>
+        <v>81.8</v>
       </c>
       <c r="N22">
-        <v>87.5</v>
+        <v>85.2</v>
       </c>
       <c r="O22">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="R22">
         <v>100</v>
       </c>
       <c r="S22">
-        <v>86.7</v>
+        <v>81.8</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4878,40 +4875,40 @@
         <v>93.3</v>
       </c>
       <c r="H23">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="L23">
         <v>100</v>
       </c>
       <c r="M23">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="N23">
+        <v>97.7</v>
+      </c>
+      <c r="O23">
+        <v>95.5</v>
+      </c>
+      <c r="P23">
+        <v>100</v>
+      </c>
+      <c r="Q23">
         <v>93.3</v>
       </c>
-      <c r="N23">
-        <v>100</v>
-      </c>
-      <c r="O23">
-        <v>100</v>
-      </c>
-      <c r="P23">
-        <v>100</v>
-      </c>
-      <c r="Q23">
-        <v>86.7</v>
-      </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>93.3</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4937,40 +4934,40 @@
         <v>90</v>
       </c>
       <c r="H24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I24">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24">
-        <v>90</v>
+        <v>94.5</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="O24">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P24">
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="R24">
         <v>100</v>
       </c>
       <c r="S24">
-        <v>90</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4996,10 +4993,10 @@
         <v>96.7</v>
       </c>
       <c r="H25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I25">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J25">
         <v>100</v>
@@ -5011,13 +5008,13 @@
         <v>100</v>
       </c>
       <c r="M25">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -5029,7 +5026,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5070,7 +5067,7 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="N26">
         <v>100</v>
@@ -5088,7 +5085,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5114,40 +5111,40 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="I27">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J27">
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N27">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="O27">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P27">
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5232,10 +5229,10 @@
         <v>100</v>
       </c>
       <c r="H29">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I29">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="J29">
         <v>100</v>
@@ -5250,10 +5247,10 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="O29">
-        <v>90</v>
+        <v>95.5</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -5291,10 +5288,10 @@
         <v>100</v>
       </c>
       <c r="H30">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J30">
         <v>100</v>
@@ -5309,10 +5306,10 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -5350,40 +5347,40 @@
         <v>96.7</v>
       </c>
       <c r="H31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="I31">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J31">
         <v>100</v>
       </c>
       <c r="K31">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="O31">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P31">
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>96.7</v>
+        <v>98.3</v>
       </c>
       <c r="R31">
         <v>100</v>
       </c>
       <c r="S31">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5409,40 +5406,40 @@
         <v>96.7</v>
       </c>
       <c r="H32">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I32">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="J32">
         <v>100</v>
       </c>
       <c r="K32">
-        <v>83.3</v>
+        <v>88.3</v>
       </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
       <c r="N32">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O32">
-        <v>90</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="P32">
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>83.3</v>
+        <v>88.3</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5527,40 +5524,40 @@
         <v>96.7</v>
       </c>
       <c r="H34">
-        <v>95</v>
+        <v>94.3</v>
       </c>
       <c r="I34">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J34">
         <v>100</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L34">
         <v>100</v>
       </c>
       <c r="M34">
+        <v>98.2</v>
+      </c>
+      <c r="N34">
+        <v>94.3</v>
+      </c>
+      <c r="O34">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="P34">
+        <v>100</v>
+      </c>
+      <c r="Q34">
         <v>96.7</v>
       </c>
-      <c r="N34">
-        <v>95</v>
-      </c>
-      <c r="O34">
-        <v>90</v>
-      </c>
-      <c r="P34">
-        <v>100</v>
-      </c>
-      <c r="Q34">
-        <v>100</v>
-      </c>
       <c r="R34">
         <v>100</v>
       </c>
       <c r="S34">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5586,40 +5583,40 @@
         <v>63.3</v>
       </c>
       <c r="H35">
-        <v>87.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I35">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="J35">
         <v>100</v>
       </c>
       <c r="K35">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="L35">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="M35">
-        <v>63.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="N35">
-        <v>87.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="O35">
-        <v>80</v>
+        <v>81.8</v>
       </c>
       <c r="P35">
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>93.3</v>
+        <v>86.7</v>
       </c>
       <c r="R35">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="S35">
-        <v>63.3</v>
+        <v>69.09999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5645,40 +5642,40 @@
         <v>90</v>
       </c>
       <c r="H36">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="I36">
+        <v>95.5</v>
+      </c>
+      <c r="J36">
+        <v>100</v>
+      </c>
+      <c r="K36">
         <v>90</v>
       </c>
-      <c r="J36">
-        <v>100</v>
-      </c>
-      <c r="K36">
-        <v>93.3</v>
-      </c>
       <c r="L36">
         <v>100</v>
       </c>
       <c r="M36">
+        <v>94.5</v>
+      </c>
+      <c r="N36">
+        <v>97.7</v>
+      </c>
+      <c r="O36">
+        <v>95.5</v>
+      </c>
+      <c r="P36">
+        <v>100</v>
+      </c>
+      <c r="Q36">
         <v>90</v>
       </c>
-      <c r="N36">
-        <v>95</v>
-      </c>
-      <c r="O36">
-        <v>90</v>
-      </c>
-      <c r="P36">
-        <v>100</v>
-      </c>
-      <c r="Q36">
-        <v>93.3</v>
-      </c>
       <c r="R36">
         <v>100</v>
       </c>
       <c r="S36">
-        <v>90</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5707,7 +5704,7 @@
         <v>100</v>
       </c>
       <c r="I37">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="J37">
         <v>100</v>
@@ -5725,7 +5722,7 @@
         <v>100</v>
       </c>
       <c r="O37">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -5763,40 +5760,40 @@
         <v>93.3</v>
       </c>
       <c r="H38">
-        <v>87.5</v>
+        <v>85.2</v>
       </c>
       <c r="I38">
-        <v>80</v>
+        <v>79.5</v>
       </c>
       <c r="J38">
         <v>100</v>
       </c>
       <c r="K38">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L38">
         <v>100</v>
       </c>
       <c r="M38">
+        <v>92.7</v>
+      </c>
+      <c r="N38">
+        <v>85.2</v>
+      </c>
+      <c r="O38">
+        <v>79.5</v>
+      </c>
+      <c r="P38">
+        <v>100</v>
+      </c>
+      <c r="Q38">
         <v>93.3</v>
       </c>
-      <c r="N38">
-        <v>87.5</v>
-      </c>
-      <c r="O38">
-        <v>80</v>
-      </c>
-      <c r="P38">
-        <v>100</v>
-      </c>
-      <c r="Q38">
-        <v>100</v>
-      </c>
       <c r="R38">
         <v>100</v>
       </c>
       <c r="S38">
-        <v>93.3</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5881,40 +5878,40 @@
         <v>100</v>
       </c>
       <c r="H40">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="I40">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J40">
         <v>100</v>
       </c>
       <c r="K40">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L40">
         <v>100</v>
       </c>
       <c r="M40">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N40">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="O40">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P40">
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R40">
         <v>100</v>
       </c>
       <c r="S40">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -5971,7 +5968,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -5980,19 +5977,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" s="2">
-        <v>78.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="G2" s="2">
-        <v>21.6</v>
+        <v>13.5</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6003,7 +6000,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -6012,19 +6009,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>86.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>13.5</v>
+        <v>8.1</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6035,7 +6032,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -6056,7 +6053,7 @@
         <v>8.1</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6152,7 +6149,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6202,7 +6199,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6234,7 +6231,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920289</v>
+        <v>20330051920235</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
@@ -6243,13 +6240,13 @@
         <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6257,7 +6254,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920289</v>
+        <v>20330051920235</v>
       </c>
       <c r="B3" t="s">
         <v>70</v>
@@ -6266,13 +6263,13 @@
         <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6280,7 +6277,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920337</v>
+        <v>21330051920307</v>
       </c>
       <c r="B4" t="s">
         <v>71</v>
@@ -6289,13 +6286,13 @@
         <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6303,7 +6300,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920337</v>
+        <v>21330051920307</v>
       </c>
       <c r="B5" t="s">
         <v>71</v>
@@ -6312,13 +6309,13 @@
         <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6332,16 +6329,16 @@
         <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6355,16 +6352,16 @@
         <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6372,22 +6369,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920292</v>
+        <v>21330051920330</v>
       </c>
       <c r="B8" t="s">
         <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6395,19 +6392,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920306</v>
+        <v>21330051920330</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
         <v>61</v>
@@ -6418,19 +6415,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920316</v>
+        <v>21330051920289</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>61</v>
@@ -6441,24 +6438,47 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920330</v>
+        <v>19330051920208</v>
       </c>
       <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920316</v>
+      </c>
+      <c r="B12" t="s">
         <v>76</v>
       </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
         <v>63</v>
       </c>
-      <c r="G11">
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6BLCM - Estadisticos 20232.xlsx
+++ b/grupos/6BLCM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -206,18 +206,18 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Ángel Martínez Gerson Hermenegildo</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
-    <t>Ángel Martínez Gerson Hermenegildo</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -230,64 +230,22 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>MORENO</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
+    <t>AGUILAR</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
+    <t>NAHOMY</t>
   </si>
   <si>
     <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>ROSA ITZEL</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
   </si>
 </sst>
 </file>
@@ -813,22 +771,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -890,22 +848,22 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -923,7 +881,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -967,22 +925,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1044,22 +1002,22 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1068,13 +1026,13 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>7</v>
       </c>
       <c r="X7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1121,22 +1079,22 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1148,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>8</v>
@@ -1198,22 +1156,22 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1275,22 +1233,22 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1302,7 +1260,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1352,22 +1310,22 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1382,10 +1340,10 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1429,22 +1387,22 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1506,31 +1464,31 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1583,22 +1541,22 @@
         <v>9</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1616,7 +1574,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1660,22 +1618,22 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1684,13 +1642,13 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>9</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -1737,22 +1695,22 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1764,10 +1722,10 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1814,22 +1772,22 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -1838,13 +1796,13 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -1891,22 +1849,22 @@
         <v>5</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -1915,16 +1873,16 @@
         <v>8</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1968,22 +1926,22 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2045,22 +2003,22 @@
         <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2078,7 +2036,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2122,22 +2080,22 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2152,7 +2110,7 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2199,28 +2157,28 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>7</v>
@@ -2229,7 +2187,7 @@
         <v>6</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2276,22 +2234,22 @@
         <v>5</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2303,13 +2261,13 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2353,22 +2311,22 @@
         <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2377,7 +2335,7 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>9</v>
@@ -2430,22 +2388,22 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2460,7 +2418,7 @@
         <v>7</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2507,22 +2465,22 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2584,22 +2542,22 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>9</v>
@@ -2608,13 +2566,13 @@
         <v>9</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>7</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2661,22 +2619,22 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2691,7 +2649,7 @@
         <v>10</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>10</v>
@@ -2738,22 +2696,22 @@
         <v>6</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
         <v>10</v>
@@ -2762,13 +2720,13 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>7</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>7</v>
@@ -2815,22 +2773,22 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -2892,22 +2850,22 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2969,22 +2927,22 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3002,7 +2960,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3046,22 +3004,22 @@
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>10</v>
@@ -3076,7 +3034,7 @@
         <v>10</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3123,22 +3081,22 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3147,16 +3105,16 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3200,22 +3158,22 @@
         <v>5</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T35">
         <v>7</v>
@@ -3230,7 +3188,7 @@
         <v>6</v>
       </c>
       <c r="X35">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -3277,22 +3235,22 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
         <v>10</v>
@@ -3354,22 +3312,22 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3431,40 +3389,40 @@
         <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T38">
         <v>7</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>7</v>
       </c>
       <c r="W38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y38">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3508,22 +3466,22 @@
         <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>10</v>
@@ -3585,22 +3543,22 @@
         <v>5</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
         <v>9</v>
@@ -3612,13 +3570,13 @@
         <v>7</v>
       </c>
       <c r="W40">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X40">
         <v>9</v>
       </c>
       <c r="Y40">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3831,22 +3789,22 @@
         <v>85.5</v>
       </c>
       <c r="N5">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="O5">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R5">
         <v>100</v>
       </c>
       <c r="S5">
-        <v>85.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3899,7 +3857,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3949,22 +3907,22 @@
         <v>94.5</v>
       </c>
       <c r="N7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O7">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P7">
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="R7">
         <v>100</v>
       </c>
       <c r="S7">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -4008,22 +3966,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N8">
-        <v>94.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O8">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="P8">
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S8">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4076,10 +4034,10 @@
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="R9">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S9">
         <v>100</v>
@@ -4126,10 +4084,10 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N10">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O10">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -4138,10 +4096,10 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S10">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4185,22 +4143,22 @@
         <v>94.5</v>
       </c>
       <c r="N11">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="O11">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R11">
         <v>100</v>
       </c>
       <c r="S11">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4244,7 +4202,7 @@
         <v>98.2</v>
       </c>
       <c r="N12">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -4259,7 +4217,7 @@
         <v>100</v>
       </c>
       <c r="S12">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4306,19 +4264,19 @@
         <v>89.8</v>
       </c>
       <c r="O13">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4362,22 +4320,22 @@
         <v>98.2</v>
       </c>
       <c r="N14">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O14">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4430,13 +4388,13 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R15">
         <v>100</v>
       </c>
       <c r="S15">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4480,22 +4438,22 @@
         <v>98.2</v>
       </c>
       <c r="N16">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O16">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R16">
         <v>100</v>
       </c>
       <c r="S16">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4598,22 +4556,22 @@
         <v>80</v>
       </c>
       <c r="N18">
-        <v>89.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="O18">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P18">
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>80</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="S18">
-        <v>80</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4657,22 +4615,22 @@
         <v>92.7</v>
       </c>
       <c r="N19">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P19">
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="R19">
         <v>100</v>
       </c>
       <c r="S19">
-        <v>92.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4716,22 +4674,22 @@
         <v>98.2</v>
       </c>
       <c r="N20">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="O20">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P20">
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>88.3</v>
+        <v>91.8</v>
       </c>
       <c r="R20">
         <v>100</v>
       </c>
       <c r="S20">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4775,22 +4733,22 @@
         <v>85.5</v>
       </c>
       <c r="N21">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="O21">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>91.7</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>85.5</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4834,22 +4792,22 @@
         <v>81.8</v>
       </c>
       <c r="N22">
-        <v>85.2</v>
+        <v>86.7</v>
       </c>
       <c r="O22">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="R22">
         <v>100</v>
       </c>
       <c r="S22">
-        <v>81.8</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4893,22 +4851,22 @@
         <v>89.09999999999999</v>
       </c>
       <c r="N23">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O23">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P23">
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>89.09999999999999</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4952,22 +4910,22 @@
         <v>94.5</v>
       </c>
       <c r="N24">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O24">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P24">
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="R24">
         <v>100</v>
       </c>
       <c r="S24">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5011,10 +4969,10 @@
         <v>98.2</v>
       </c>
       <c r="N25">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O25">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P25">
         <v>100</v>
@@ -5026,7 +4984,7 @@
         <v>100</v>
       </c>
       <c r="S25">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5085,7 +5043,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5129,22 +5087,22 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N27">
-        <v>94.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O27">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P27">
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5247,10 +5205,10 @@
         <v>100</v>
       </c>
       <c r="N29">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O29">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P29">
         <v>100</v>
@@ -5306,10 +5264,10 @@
         <v>100</v>
       </c>
       <c r="N30">
-        <v>96.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="O30">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="P30">
         <v>100</v>
@@ -5365,22 +5323,22 @@
         <v>98.2</v>
       </c>
       <c r="N31">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="O31">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P31">
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>98.3</v>
+        <v>98.8</v>
       </c>
       <c r="R31">
         <v>100</v>
       </c>
       <c r="S31">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5424,22 +5382,22 @@
         <v>98.2</v>
       </c>
       <c r="N32">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O32">
-        <v>86.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P32">
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>88.3</v>
+        <v>91.8</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5542,22 +5500,22 @@
         <v>98.2</v>
       </c>
       <c r="N34">
-        <v>94.3</v>
+        <v>94.5</v>
       </c>
       <c r="O34">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="P34">
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R34">
         <v>100</v>
       </c>
       <c r="S34">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5601,22 +5559,22 @@
         <v>69.09999999999999</v>
       </c>
       <c r="N35">
-        <v>84.09999999999999</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="O35">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P35">
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>86.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R35">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="S35">
-        <v>69.09999999999999</v>
+        <v>78.8</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5660,22 +5618,22 @@
         <v>94.5</v>
       </c>
       <c r="N36">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="O36">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="P36">
         <v>100</v>
       </c>
       <c r="Q36">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R36">
         <v>100</v>
       </c>
       <c r="S36">
-        <v>94.5</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5722,7 +5680,7 @@
         <v>100</v>
       </c>
       <c r="O37">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P37">
         <v>100</v>
@@ -5778,22 +5736,22 @@
         <v>92.7</v>
       </c>
       <c r="N38">
-        <v>85.2</v>
+        <v>89.8</v>
       </c>
       <c r="O38">
-        <v>79.5</v>
+        <v>82.8</v>
       </c>
       <c r="P38">
         <v>100</v>
       </c>
       <c r="Q38">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="R38">
         <v>100</v>
       </c>
       <c r="S38">
-        <v>92.7</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5896,22 +5854,22 @@
         <v>96.40000000000001</v>
       </c>
       <c r="N40">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
       <c r="O40">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="P40">
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>90</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R40">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="S40">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
   </sheetData>
@@ -5977,19 +5935,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>86.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6000,7 +5958,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -6009,19 +5967,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6032,28 +5990,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4">
         <v>37</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6064,10 +6022,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C5">
         <v>37</v>
@@ -6085,7 +6043,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6096,7 +6054,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>64</v>
@@ -6117,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6128,7 +6086,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
@@ -6149,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6199,7 +6157,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6231,22 +6189,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920235</v>
+        <v>19330051920208</v>
       </c>
       <c r="B2" t="s">
         <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6254,231 +6212,24 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920235</v>
+        <v>21330051920323</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920307</v>
-      </c>
-      <c r="B4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920307</v>
-      </c>
-      <c r="B5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920323</v>
-      </c>
-      <c r="B6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920323</v>
-      </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920330</v>
-      </c>
-      <c r="B8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C8" t="s">
-        <v>79</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920330</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920289</v>
-      </c>
-      <c r="B10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920208</v>
-      </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920316</v>
-      </c>
-      <c r="B12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>
